--- a/Data/Input/Tracker/3043_Latam_DataLoad_Tracker 2026_07.xlsx
+++ b/Data/Input/Tracker/3043_Latam_DataLoad_Tracker 2026_07.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aws-svc-rpa52d\Documents\UiPath\3043_LATAM_DataLoad\Data\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aws-svc-rpa52d\Documents\UiPath\3043_LATAM_DataLoad\Data\Input\Tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E4045D-66F9-4A5E-9815-662B06ABD27C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8541E4C5-7FB0-42FB-B693-475644ECFD8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{53B33B9B-9600-4544-943F-760533730144}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{53B33B9B-9600-4544-943F-760533730144}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenue_Tracker" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
   <si>
     <t>Revenue Validation</t>
   </si>
@@ -114,24 +114,7 @@
     <t>Brazil TP</t>
   </si>
   <si>
-    <t>Pass</t>
-  </si>
-  <si>
     <t>Currency &amp; Rate Population</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Hold</t>
-  </si>
-  <si>
-    <t>Country | Row Number | Column Name | Invalid Value | Exception Details
-Argentina | 11 | EL2 | Invalid EL2 Value | EL2 value does not meet the required validation rule
-Argentina | 11 | EL2 Name | NULL/N/A | EL2 Name value is missing or not available
-Argentina | 13 | Category | Invalid Category | Category is not available in approved list
-Argentina | 15 | Code | 40900 | Code is not mapped with PDD Services
-Argentina | 15 | EL3 Name | Product Mapping Issue | Product does not align with the respective sub-product mapping</t>
   </si>
   <si>
     <t>Pre-validation Status</t>
@@ -260,21 +243,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -633,11 +616,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
     </row>
     <row r="2" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -656,7 +639,7 @@
         <v>5</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>6</v>
@@ -696,54 +679,22 @@
       <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>28</v>
-      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="6"/>
     </row>
     <row r="4" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -898,8 +849,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>34</v>
+      <c r="A1" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -916,34 +867,34 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -951,91 +902,91 @@
       <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
     </row>
     <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
